--- a/docs/notices/CAHIER_RECETTE_AUDITS_2026-10-26_resultats_Claude.xlsx
+++ b/docs/notices/CAHIER_RECETTE_AUDITS_2026-10-26_resultats_Claude.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="664">
   <si>
     <t>Cahier de recette : corrections des audits de code</t>
   </si>
@@ -28,7 +28,7 @@
     <t>Version testée</t>
   </si>
   <si>
-    <t>Branche PRES-/audits-code-dffa0a, commit 9b02b3c7 (26/10/2026). WAR : target/prestige.war construit à partir de ce commit. Il ne contient pas les commits récents de la branche principale (droits, horloge, bornes, téléphone de la vente).</t>
+    <t>Branche PRES-/audits-code-dffa0a, état du 26/10/2026 au soir (dates VC-12 et VC-16 comprises). WAR : target/prestige.war construit à partir de cet état. Il ne contient pas les commits récents de la branche principale (droits, horloge, bornes, téléphone de la vente).</t>
   </si>
   <si>
     <t>Référence</t>
@@ -79,10 +79,10 @@
     <t>Colonne « Test automatique » : script Playwright du dépôt (src/test/e2e/...), lancé seul, un à la fois : node src/test/e2e/audits/repro-vente-comptant.js. Une ligne FAIL = défaut présent.</t>
   </si>
   <si>
-    <t>Restent en échec</t>
-  </si>
-  <si>
-    <t>VC-12 et VC-16 (cas « hier ») : décision métier en attente sur la date des écritures. Voir l'onglet « Décisions ».</t>
+    <t>Dates des écritures</t>
+  </si>
+  <si>
+    <t>VC-12 et VC-16 : décision du 26/10, les écritures portent la date de l'opération réelle (vente d'origine, date saisie du mouvement).</t>
   </si>
   <si>
     <t>Exemple de saisie</t>
@@ -411,13 +411,13 @@
 3. Comparer les dates de la transaction, de la contre-passation, de la recette et du mouvement de stock.</t>
   </si>
   <si>
-    <t>DÉCISION EN ATTENTE (date de l'opération ou de la saisie) : non corrigé. À jouer pour constat seulement.</t>
+    <t>Toutes les écritures portent la date de la vente d'origine (veille) : transaction de la copie, contre-passation, recette, mouvements de stock de la copie et de l'annulation (décision du 26/10 : date de l'opération réelle). Une modification du jour même reste datée du jour.</t>
   </si>
   <si>
     <t>Transaction et contre-passation datées de la veille ; recette et stock du jour.</t>
   </si>
   <si>
-    <t>repro-vente-comptant.js (VC-12) : reste en échec tant que la décision n'est pas prise</t>
+    <t>repro-vente-comptant.js (VC-12)</t>
   </si>
   <si>
     <t>11</t>
@@ -463,13 +463,13 @@
 2. Puis une entrée de 1 000 F datée d'hier.</t>
   </si>
   <si>
-    <t>Date de demain refusée. Date d'hier : DÉCISION EN ATTENTE (aujourd'hui, mouvement et règlement à hier, transaction au jour).</t>
+    <t>Date de demain refusée avec un message. Date d'hier : mouvement, règlement et transaction de caisse datés d'hier (décision du 26/10 : date saisie du mouvement).</t>
   </si>
   <si>
     <t>Date future acceptée ; dates différentes entre mouvement, règlement et transaction.</t>
   </si>
   <si>
-    <t>repro-remise-caisse.js (VC-16) : le cas « hier » reste en échec tant que la décision n'est pas prise</t>
+    <t>repro-remise-caisse.js (VC-16)</t>
   </si>
   <si>
     <t>13</t>
@@ -1743,10 +1743,7 @@
     <t>VC-12, VC-16</t>
   </si>
   <si>
-    <t>Seules les dates futures sont refusées. Une modification d'une vente de la veille et un mouvement daté d'hier gardent des dates différentes selon l'écriture.</t>
-  </si>
-  <si>
-    <t>Date de l'opération réelle, ou date de la saisie ?</t>
+    <t>Tranché le 26/10 : date de l'opération réelle. Modification d'une vente d'un autre jour : toutes les écritures à la date de la vente d'origine ; mouvement de caisse : date saisie (le futur est refusé).</t>
   </si>
   <si>
     <t>Vente différée réglée puis modifiée</t>
@@ -1803,8 +1800,8 @@
     <t>Faut-il ajouter un verrou malgré tout ?</t>
   </si>
   <si>
-    <t>Réussi : VC-01 précondition : vente comptant de 2 boîtes encaissée  [4c8ce3c2-ce74-43c6-a51e-0bc9b63a8b34]
-Réussi : VC-01 attendu : modifier la quantité d'une ligne d'une vente encaissée est refusé, ligne inchangée (2 boîtes)  [réponse {"msg":"Cette vente (N° 261026_00268) a été clôturée le 26/10/2026 19:36 : elle ne peut plus être modifiée ici. Pour retirer un produit, passez par « Ventes ter ; ligne après = qté|montant 2|6950 ; vente {"statut":"is_Closed","annulee":false,"prix":6950,"remise":0,"partClient":0,"tva":0,"client":"NU…</t>
+    <t>Réussi : VC-01 précondition : vente comptant de 2 boîtes encaissée  [025b5e25-810d-4edf-8d55-aad8237df96c]
+Réussi : VC-01 attendu : modifier la quantité d'une ligne d'une vente encaissée est refusé, ligne inchangée (2 boîtes)  [réponse {"msg":"Cette vente (N° 261026_00417) a été clôturée le 26/10/2026 19:59 : elle ne peut plus être modifiée ici. Pour retirer un produit, passez par « Ventes ter ; ligne après = qté|montant 2|6950 ; vente {"statut":"is_Closed","annulee":false,"prix":6950,"remise":0,"partClient":0,"tva":0,"client":"NU…</t>
   </si>
   <si>
     <t>Claude (tests automatiques)</t>
@@ -1813,23 +1810,23 @@
     <t>26/10/2026</t>
   </si>
   <si>
-    <t>Test automatique repro-vente-comptant.js, 26/10/2026 19:35-19:45 : 2 réussi(s), 0 en échec</t>
-  </si>
-  <si>
-    <t>Réussi : VC-02 attendu : « Terminer la prévente » sur une vente encaissée est refusé, statut is_Closed conservé  [réponse {"msg":"Cette vente (N° 261026_00269) a été clôturée le 26/10/2026 19:36 : elle ne peut plus être modifiée ici. Pour ret ; statut après is_Closed ; transactions de caisse 1]</t>
-  </si>
-  <si>
-    <t>Test automatique repro-vente-comptant.js, 26/10/2026 19:35-19:45 : 1 réussi(s), 0 en échec</t>
-  </si>
-  <si>
-    <t>Réussi : VC-04 précondition : modification ouverte (copie en cours)  [{"msg":"Opération effectuée avec success","data":{"lgPREENREGISTREMENTID":"a923845f-86f8-4a9b-a563-9b98c08518bd","intPRICE":3475,"intPRICEREMISE":0,"strREF":"26]
+    <t>Test automatique repro-vente-comptant.js, 26/10/2026 19:35-20:05 : 2 réussi(s), 0 en échec</t>
+  </si>
+  <si>
+    <t>Réussi : VC-02 attendu : « Terminer la prévente » sur une vente encaissée est refusé, statut is_Closed conservé  [réponse {"msg":"Cette vente (N° 261026_00418) a été clôturée le 26/10/2026 19:59 : elle ne peut plus être modifiée ici. Pour ret ; statut après is_Closed ; transactions de caisse 1]</t>
+  </si>
+  <si>
+    <t>Test automatique repro-vente-comptant.js, 26/10/2026 19:35-20:05 : 1 réussi(s), 0 en échec</t>
+  </si>
+  <si>
+    <t>Réussi : VC-04 précondition : modification ouverte (copie en cours)  [{"msg":"Opération effectuée avec success","data":{"lgPREENREGISTREMENTID":"5fcc013e-b026-4deb-9601-648de88a6afa","intPRICE":3475,"intPRICEREMISE":0,"strREF":"26]
 Réussi : VC-04 attendu : annuler la vente pendant sa modification est refusé, ou la clôture de la copie ne la réannule pas (une seule annulation ; stock = stock de départ − 1 car la copie est vendue)  [annulation {"msg":"Cette vente est en cours de modification : terminez ou abandonnez la mod ; clôture copie {"s":true,"m":"Opération effectuée avec success"} ; annulations de l'origine 1 ; stock départ 97 → fin 96 ; somme caiss…</t>
   </si>
   <si>
     <t>Réussi : VC-05 attendu : TVA de la vente = somme des TVA des lignes  [clôture true ; TVA en-tête 499 ; somme des lignes 499 ; TVA du mouvement de caisse 499]</t>
   </si>
   <si>
-    <t>Test automatique repro-remise-caisse.js, 26/10/2026 19:35-19:45 : 1 réussi(s), 0 en échec</t>
+    <t>Test automatique repro-remise-caisse.js, 26/10/2026 19:35-20:05 : 1 réussi(s), 0 en échec</t>
   </si>
   <si>
     <t>Réussi : VC-06 attendu : une vente encaissée au net sans remise n'enregistre pas de remise (remise de la vente = 0)  [net demandé sans remiseId 3270 (plein tarif 3270) ; clôture true ; remise enregistrée sur la vente 0 ; transaction montant|remise|payé 3270|0|3270]</t>
@@ -1839,14 +1836,14 @@
 Réussi : VC-07 attendu : la remise enregistrée est celle affichée et encaissée (prix − remise = net payé)  [remise affichée 325 ; net affiché 2945 ; remise enregistrée (vente) 325 ; prix − remise enregistrée 2945 ; transaction remise|net|payé 325|2945|2945]</t>
   </si>
   <si>
-    <t>Test automatique repro-remise-caisse.js, 26/10/2026 19:35-19:45 : 2 réussi(s), 0 en échec</t>
+    <t>Test automatique repro-remise-caisse.js, 26/10/2026 19:35-20:05 : 2 réussi(s), 0 en échec</t>
   </si>
   <si>
     <t>Réussi : VC-08 précondition : vente encaissée rattachée au client d'essai  [{"statut":"is_Closed","annulee":false,"prix":3475,"remise":0,"partClient":0,"tva":0,"client":"ZZAUDIT-CL-VC08"}]
-Réussi : VC-08 attendu : changer le client d'une vente encaissée (identifiant inconnu) est refusé, client conservé  [réponse {"msg":"Cette vente (N° 261026_00272) a été clôturée le 26/10/2026 19:36 : elle ne peut plus être modifiée ici. Pour ret ; client après ZZAUDIT-CL-VC08]</t>
-  </si>
-  <si>
-    <t>Réussi : VC-09 précondition : deux ventes en cours de 1 boîte chacune, stock 1, FORCER_STOCK_VENTE = 0  [af947d3d-f2fb-4a6e-9ca2-35af72429c04 / dda46ad3-e694-45c6-a19a-aa1e47c77f64]
+Réussi : VC-08 attendu : changer le client d'une vente encaissée (identifiant inconnu) est refusé, client conservé  [réponse {"msg":"Cette vente (N° 261026_00421) a été clôturée le 26/10/2026 19:59 : elle ne peut plus être modifiée ici. Pour ret ; client après ZZAUDIT-CL-VC08]</t>
+  </si>
+  <si>
+    <t>Réussi : VC-09 précondition : deux ventes en cours de 1 boîte chacune, stock 1, FORCER_STOCK_VENTE = 0  [ff3a413a-994c-40e2-980a-83fbd27cc79c / 6611c3fe-6312-45da-8836-6084ad317a59]
 Réussi : VC-09 attendu : la seconde validation est refusée, le stock ne passe pas sous zéro  [clôture 1 true ; clôture 2 {"s":false,"m":"Impossible de valider la vente : stock insuffisant pour A CIN 500MG CPR PELL B/3 (une autre vente l'a peut-être pris entre-temps). Veuillez modifier la vente."} ; stock final 0]</t>
   </si>
   <si>
@@ -1854,20 +1851,14 @@
 Réussi : VC-11 attendu : l'annulation rend les 2 boîtes au lot B d'où elles sont sorties (A=0, B=5)  [annulation true ; lots après annulation ZZAUDIT-LOT-A=0,ZZAUDIT-LOT-B=5]</t>
   </si>
   <si>
-    <t>ÉCHEC : VC-12 attendu : toutes les écritures de la modification d'une vente d'hier portent la même date  [clôture copie true ; transaction de la copie 2026-10-25 ; contre-passation 2026-10-25,2026-10-25 ; recette de la copie 2026-10-26 ; mouvement de stock de la copie 2026-10-26 ; aujourd'hui 2026-10-26]</t>
-  </si>
-  <si>
-    <t>Test automatique repro-vente-comptant.js, 26/10/2026 19:35-19:45 : 0 réussi(s), 1 en échec. Écart attendu : décision métier en attente sur la date des écritures (onglet Décisions), rien n'a été changé</t>
+    <t>Réussi : VC-12 attendu : toutes les écritures de la modification d'une vente d'hier portent la même date  [clôture copie true ; transaction de la copie 2026-10-25 ; contre-passation 2026-10-25,2026-10-25 ; recette de la copie 2026-10-25 ; mouvement de stock de la copie 2026-10-25 ; mouvement de stock de l'annulation 2026-10-25,2026-10-25 ; aujourd'hui 2026-10-26]</t>
   </si>
   <si>
     <t>Réussi : VC-14 attendu : une clôture qui déclare 1 F payé pour une vente de 6950 F est refusée  [clôture {"s":false,"m":"Le montant réglé (1 F) est inférieur au net de la vente (6950 F) : vérifiez les montants saisis, ou choisissez le règlement en différé."} ; transaction montant|net|payé|réglé  ; recette aucune]</t>
   </si>
   <si>
-    <t>ÉCHEC : VC-16 attendu : un mouvement de caisse saisi à la date d'hier porte la même date dans le mouvement, le règlement et la transaction  [{"msg":"Opération effectuée .","mvtId":"c9e4721a-3d9c-40ba-ad98-915246f36bb7","success":true,"http": ; mouvement 2026-10-25 | r�glement 2026-10-25 | transaction 2026-10-26]
+    <t>Réussi : VC-16 attendu : un mouvement de caisse saisi à la date d'hier porte la même date dans le mouvement, le règlement et la transaction  [{"msg":"Opération effectuée .","mvtId":"32375fa3-024e-4e34-a341-805d92350258","success":true,"http": ; mouvement 2026-10-25 | r�glement 2026-10-25 | transaction 2026-10-25]
 Réussi : VC-16 attendu : un mouvement de caisse daté de demain est refusé  [{"msg":"La date du mouvement ne peut pas être dans le futur.","success":false,"http":200}]</t>
-  </si>
-  <si>
-    <t>Test automatique repro-remise-caisse.js, 26/10/2026 19:35-19:45 : 1 réussi(s), 1 en échec. Le cas « date de demain » est refusé comme attendu ; le cas « hier » reste en échec : décision métier en attente (onglet Décisions)</t>
   </si>
   <si>
     <t>Réussi : N1 attendu : une annulation qui échoue (produit sans ligne de stock dans l'emplacement) ne laisse aucune écriture  [réponse {"msg":"Annulation impossible : le produit A CIN 500MG CPR PELL B/3 n'a pas de ligne de stock dans l'emplacement de la v ; vente annulée ? false ; copies d'annulation 0 ; contre-passations 0]</t>
@@ -1880,7 +1871,7 @@
 Réussi : CR-01 attendu : après annulation, l'encours revient à 0  [annulation true ; encours organisme 564 → 0 ; encours client 564 → 0]</t>
   </si>
   <si>
-    <t>Test automatique repro-vente-assurance.js, 26/10/2026 19:35-19:45 : 2 réussi(s), 0 en échec</t>
+    <t>Test automatique repro-vente-assurance.js, 26/10/2026 19:35-20:05 : 2 réussi(s), 0 en échec</t>
   </si>
   <si>
     <t>Réussi : CR-02 précondition : modification ouverte  [1dd5aee8-1a73-45ae-a79c-d9ce16c3db6b]
@@ -1895,13 +1886,13 @@
 Réussi : CR-05 attendu : en espèces, le montant réglé de la transaction = montant payé par le client (net arrondi de la part client 362)  [prix 2010 ; remise 40 ; parts TP 1608 ; part client 362 ; transaction payé|réglé|remise 360|360|40]</t>
   </si>
   <si>
-    <t>Test automatique repro-vo-remise.js, 26/10/2026 19:35-19:45 : 2 réussi(s), 0 en échec</t>
+    <t>Test automatique repro-vo-remise.js, 26/10/2026 19:35-20:05 : 2 réussi(s), 0 en échec</t>
   </si>
   <si>
     <t>Réussi : N3 attendu : en différé sans acompte, la dette du client = part client (362)  [part client 362 ; remise 40 ; dette prix|reste 362|362]</t>
   </si>
   <si>
-    <t>Test automatique repro-vo-remise.js, 26/10/2026 19:35-19:45 : 1 réussi(s), 0 en échec</t>
+    <t>Test automatique repro-vo-remise.js, 26/10/2026 19:35-20:05 : 1 réussi(s), 0 en échec</t>
   </si>
   <si>
     <t>Réussi : CR-06 attendu : avec une remise (10 %) supérieure à la part client (5 %), parts TP + part client = prix − remise  [prix 2010 ; remise 10 ; parts TP 1909 ; part client 91 ; total 2000 (attendu 2000)]</t>
@@ -1910,7 +1901,7 @@
     <t>Réussi : CR-07 attendu : une part de 1 F et un taux de 1 % renvoyés par le poste (calcul serveur : 80 %) sont refusés, ou ignorés au profit du calcul serveur  [clôture true ; part calculée [] ; ligne enregistrée ZZAUDIT-TP-CR07/80/564/is_Closed/unpaid ; encours organisme 564]</t>
   </si>
   <si>
-    <t>Test automatique repro-vente-assurance.js, 26/10/2026 19:35-19:45 : 1 réussi(s), 0 en échec</t>
+    <t>Test automatique repro-vente-assurance.js, 26/10/2026 19:35-20:05 : 1 réussi(s), 0 en échec</t>
   </si>
   <si>
     <t>Réussi : CR-09 attendu : ajouter un tiers payant à 250 % est refusé  [réponse {"msg":"Le taux du tiers payant doit être compris entre 0 et 100 %.","success":false,"http":200} ; lignes ZZAUDIT-TP-CR09A/70/0/is_Process/unpaid]</t>
@@ -1924,7 +1915,7 @@
 Réussi : CA-03 remise en état : une vente ordinaire après une vente « dépôt » n'est plus enregistrée comme exclue</t>
   </si>
   <si>
-    <t>Test automatique repro-vente-assurance.js, 26/10/2026 19:35-19:45 : 3 réussi(s), 0 en échec</t>
+    <t>Test automatique repro-vente-assurance.js, 26/10/2026 19:35-20:05 : 3 réussi(s), 0 en échec</t>
   </si>
   <si>
     <t>Réussi : CA-09 attendu : la part passe de l'organisme A à l'organisme B (encours A 564 → 0, B 0 → 564)  [réponse {"msg":"Opération effectuée avec succèss","success":true,"refId":"d1353385-22c4-412e-afc6-fc71f735a8 ; encours A 0 ; encours B 564 ; lignes ZZAUDIT-TP-CA09B/80/564/is_Closed/unpaid]</t>
@@ -1946,7 +1937,7 @@
 Réussi : CA-06 attendu : un règlement de carnet dépôt de −1 000 F est refusé, solde inchangé  [réponse {"msg":"Le montant du règlement doit être supérieur à zéro.","success":false,"http":200} ; solde 5000 → 5000]</t>
   </si>
   <si>
-    <t>Test automatique repro-carnet.js, 26/10/2026 19:35-19:45 : 2 réussi(s), 0 en échec</t>
+    <t>Test automatique repro-carnet.js, 26/10/2026 19:35-20:05 : 2 réussi(s), 0 en échec</t>
   </si>
   <si>
     <t>Réussi : CA-07 précondition : retour carnet de 2 boîtes créé (stock 100)  [{"data":{"id":7515},"success":true,"http":200}]
@@ -1956,7 +1947,7 @@
     <t>Réussi : CA-08 attendu : un retour de −3 boîtes est refusé  [réponse {"msg":"La quantité retournée doit être supérieure à zéro.","success":false,"http":200} ; stock 102 → 102]</t>
   </si>
   <si>
-    <t>Test automatique repro-carnet.js, 26/10/2026 19:35-19:45 : 1 réussi(s), 0 en échec</t>
+    <t>Test automatique repro-carnet.js, 26/10/2026 19:35-20:05 : 1 réussi(s), 0 en échec</t>
   </si>
   <si>
     <t>Réussi : CA-15 attendu : un retour sans motif est refusé avec un message (pas une erreur 500)  [HTTP 200 ; {"msg":"Choisissez le motif du retour.","success":false,"http":200}]</t>
@@ -1972,13 +1963,13 @@
 Réussi : CA-12 attendu : l'historique de stock du retour enchaîne (début + quantité = fin) et n'est écrit qu'une fois  [mouvements : 100+2=102]</t>
   </si>
   <si>
-    <t>Test automatique repro-carnet.js, 26/10/2026 19:35-19:45 : 4 réussi(s), 0 en échec</t>
+    <t>Test automatique repro-carnet.js, 26/10/2026 19:35-20:05 : 4 réussi(s), 0 en échec</t>
   </si>
   <si>
     <t>Réussi : F1 attendu : supprimer une facture définitive par DELETE facturation/{id} est refusé (ou ses bons redeviennent facturables)  [HTTP 200 ; facture encore en base ? 1 ; statut du bon charged ; factures définitives restantes portant le bon : 6220]</t>
   </si>
   <si>
-    <t>Test automatique repro-facturation.js, 26/10/2026 19:35-19:45 : 1 réussi(s), 0 en échec</t>
+    <t>Test automatique repro-facturation.js, 26/10/2026 19:35-20:05 : 1 réussi(s), 0 en échec</t>
   </si>
   <si>
     <t>Réussi : F2 précondition : facture définitive générée, bon marqué « charged »  [{"status":1,"http":200} ; statut charged ; factures 6220]
@@ -1986,7 +1977,7 @@
 Réussi : F2 attendu (provisoire) : un bon déjà facturé n'entre pas dans une facture provisoire  [génération provisoire {"success":true,"http":200} ; provisoires portant le bon : ]</t>
   </si>
   <si>
-    <t>Test automatique repro-facturation.js, 26/10/2026 19:35-19:45 : 3 réussi(s), 0 en échec</t>
+    <t>Test automatique repro-facturation.js, 26/10/2026 19:35-20:05 : 3 réussi(s), 0 en échec</t>
   </si>
   <si>
     <t>Réussi : F3 attendu : 5 paires de générations simultanées produisent toujours deux numéros différents  [0 paire(s) sur 5 avec le même numéro : 6221,6222 ; 6223,6224 ; 6225,6226 ; 6227,6228 ; 6229,6230]</t>
@@ -1998,7 +1989,7 @@
     <t>Réussi : N8 attendu : un client assuré créé avec succès par l'écran existe en base (client / compte / ayant droit = 1 / 1 / 1)  [réponse succès, identifiant ebbca99d-c945-407b-a45c-7c94f9a6db3c ; en base client / compte / ayant droit : 1 / 1 / 1]</t>
   </si>
   <si>
-    <t>Test automatique repro-assurances-liens.js, 26/10/2026 19:35-19:45 : 1 réussi(s), 0 en échec</t>
+    <t>Test automatique repro-assurances-liens.js, 26/10/2026 19:35-20:05 : 1 réussi(s), 0 en échec</t>
   </si>
   <si>
     <t>Réussi : M1 attendu : associer un carnet à un client assuré garde son assurance active et RO, le carnet n'est pas RO  [réponse {"data":{"strLASTNAME":"ZZAUDIT M1","lgTIERSPAYANTID":"ZZAUDIT-TP-M1A","fullName ; liens avant M1A/enable/RO=1/prio=1 ; après M1A/enable/RO=1/prio=1 ; M1K/enable/RO=0/prio=2]</t>
@@ -2008,7 +1999,7 @@
 Réussi : M2 attendu (case « principal » non cochée) : un seul RO actif après le changement d'organisme  [réponse {"msg":"Opération effectuée avec succèss","success":true,"refId":"b9766d72-1194- ; RO actifs 1 ; liens M2bA/enable/RO=1/prio=1 ; M2bB/enable/RO=0/prio=2]</t>
   </si>
   <si>
-    <t>Test automatique repro-assurances-liens.js, 26/10/2026 19:35-19:45 : 2 réussi(s), 0 en échec</t>
+    <t>Test automatique repro-assurances-liens.js, 26/10/2026 19:35-20:05 : 2 réussi(s), 0 en échec</t>
   </si>
   <si>
     <t>Réussi : M3 attendu : la complémentaire C remplaçant un lien supprimé est créée active avec une priorité ≥ 1, sans hériter du lien supprimé  [réponse {"msg":"Opération effectuée avec succèss","success":true,"refId":"7d267fc8-5505- ; liens M3A/enable/RO=1/prio=1 ; M3C/enable/RO=0/prio=2 ; M3B/delete/RO=0/prio=-1]
@@ -2022,14 +2013,14 @@
     <t>Réussi : DIF-01 attendu : un règlement fait pendant la modification est refusé, ou déduit de la dette de la copie (caisse + dette = prix)  [règlement pendant modification {"s":false,"m":"Une des ventes choisies a été annulée ou modifiée : rechargez la liste."} ; clôture copie true ; dette restante 5510 + réglé 0 = 5510 (prix 5510)]</t>
   </si>
   <si>
-    <t>Test automatique repro-differes.js, 26/10/2026 19:35-19:45 : 1 réussi(s), 0 en échec</t>
+    <t>Test automatique repro-differes.js, 26/10/2026 19:35-20:05 : 1 réussi(s), 0 en échec</t>
   </si>
   <si>
     <t>Réussi : DIF-02 précondition : vente différée de 5510 avec 2755 d'acompte ; caisse + dette = prix  [caisse 2755 ; dette 2755]
 Réussi : DIF-02 attendu : après modification sans changement (copie en différé, 0 reçu), caisse + dette = prix  [clôture copie true ; caisse nette 0 + dette 5510 = 5510 (prix 5510)]</t>
   </si>
   <si>
-    <t>Test automatique repro-differes.js, 26/10/2026 19:35-19:45 : 2 réussi(s), 0 en échec</t>
+    <t>Test automatique repro-differes.js, 26/10/2026 19:35-20:05 : 2 réussi(s), 0 en échec</t>
   </si>
   <si>
     <t>Réussi : DIF-03 attendu : vente déjà réglée de 2755 puis passée à un autre client : refus, ou règlement reporté (dettes + réglé = prix)  [clôture copie false ; dette client 1 2755 ; dette client 2 0 ; réglé par le client 1 2755 ; total 5510 (prix 5510)]</t>
@@ -2062,7 +2053,7 @@
     <t>11 contrôle(s) réussi(s), 0 en échec.</t>
   </si>
   <si>
-    <t>Test automatique test-annulation-vente-double.js, 26/10/2026 19:35-19:45 : 11 réussi(s), 0 en échec</t>
+    <t>Test automatique test-annulation-vente-double.js, 26/10/2026 19:35-20:05 : 11 réussi(s), 0 en échec</t>
   </si>
   <si>
     <t>54 contrôle(s) réussi(s), 2 en échec.
@@ -2070,10 +2061,10 @@
 ÉCHEC : PDF : titre et période, client, lignes (ventes, règlement, fin de mois), totaux = écran</t>
   </si>
   <si>
-    <t>Test automatique test-differes-modification, test-differes-reglement, test-differes-solde, test-differe-nom-client.js, 26/10/2026 19:35-19:45 : 54 réussi(s), 2 en échec. Environnement du poste : les 2 échecs portent sur l'ouverture du PDF par le navigateur de test (Chromium sans écran télécharge le PDF au lieu d'exposer son adresse). Le PDF produit par le serveur a été lu à part le 26/10 : titre, client, lignes et totaux conformes à l'écran</t>
-  </si>
-  <si>
-    <t>Test automatique test-mvt-caisse.js, 26/10/2026 19:35-19:45 : 11 réussi(s), 0 en échec</t>
+    <t>Test automatique test-differes-modification, test-differes-reglement, test-differes-solde, test-differe-nom-client.js, 26/10/2026 19:35-20:05 : 54 réussi(s), 2 en échec. Environnement du poste : les 2 échecs portent sur l'ouverture du PDF par le navigateur de test (Chromium sans écran télécharge le PDF au lieu d'exposer son adresse). Le PDF produit par le serveur a été lu à part le 26/10 : titre, client, lignes et totaux conformes à l'écran</t>
+  </si>
+  <si>
+    <t>Test automatique test-mvt-caisse.js, 26/10/2026 19:35-20:05 : 11 réussi(s), 0 en échec</t>
   </si>
   <si>
     <t>9 contrôle(s) réussi(s), 6 en échec.
@@ -2085,22 +2076,22 @@
 ÉCHEC : B. Dépôt : dernière ligne = stock réel du dépôt  [undefined / 0]</t>
   </si>
   <si>
-    <t>Test automatique test-historique-deconditionnement.js, 26/10/2026 19:35-19:45 : 9 réussi(s), 6 en échec. Environnement du poste : la partie A (officine) passe en entier ; la partie B demande un dépôt de type 2, absent de la base de test (0 dépôt)</t>
+    <t>Test automatique test-historique-deconditionnement.js, 26/10/2026 19:35-20:05 : 9 réussi(s), 6 en échec. Environnement du poste : la partie A (officine) passe en entier ; la partie B demande un dépôt de type 2, absent de la base de test (0 dépôt)</t>
   </si>
   <si>
     <t>21 contrôle(s) réussi(s), 0 en échec.</t>
   </si>
   <si>
-    <t>Test automatique test-deuxieme-assurance, test-vente-changer-tiers-payant.js, 26/10/2026 19:35-19:45 : 21 réussi(s), 0 en échec</t>
+    <t>Test automatique test-deuxieme-assurance, test-vente-changer-tiers-payant.js, 26/10/2026 19:35-20:05 : 21 réussi(s), 0 en échec</t>
   </si>
   <si>
     <t>33 contrôle(s) réussi(s), 0 en échec.</t>
   </si>
   <si>
-    <t>Test automatique test-facturation-carnet-depot.js, 26/10/2026 19:35-19:45 : 33 réussi(s), 0 en échec</t>
-  </si>
-  <si>
-    <t>Test automatique test-client-credit-course, test-mode-reglement-client.js, 26/10/2026 19:35-19:45 : 33 réussi(s), 0 en échec</t>
+    <t>Test automatique test-facturation-carnet-depot.js, 26/10/2026 19:35-20:05 : 33 réussi(s), 0 en échec</t>
+  </si>
+  <si>
+    <t>Test automatique test-client-credit-course, test-mode-reglement-client.js, 26/10/2026 19:35-20:05 : 33 réussi(s), 0 en échec</t>
   </si>
 </sst>
 </file>
@@ -2520,19 +2511,19 @@
         <v>51</v>
       </c>
       <c r="K2" t="s" s="6">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="L2" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M2" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N2" t="s" s="6">
+        <v>579</v>
+      </c>
+      <c r="O2" t="s" s="6">
         <v>580</v>
-      </c>
-      <c r="O2" t="s" s="6">
-        <v>581</v>
       </c>
     </row>
     <row r="3">
@@ -2567,19 +2558,19 @@
         <v>61</v>
       </c>
       <c r="K3" t="s" s="6">
+        <v>581</v>
+      </c>
+      <c r="L3" t="s" s="6">
+        <v>25</v>
+      </c>
+      <c r="M3" t="s" s="6">
+        <v>578</v>
+      </c>
+      <c r="N3" t="s" s="6">
+        <v>579</v>
+      </c>
+      <c r="O3" t="s" s="6">
         <v>582</v>
-      </c>
-      <c r="L3" t="s" s="6">
-        <v>25</v>
-      </c>
-      <c r="M3" t="s" s="6">
-        <v>579</v>
-      </c>
-      <c r="N3" t="s" s="6">
-        <v>580</v>
-      </c>
-      <c r="O3" t="s" s="6">
-        <v>583</v>
       </c>
     </row>
     <row r="4">
@@ -2614,19 +2605,19 @@
         <v>69</v>
       </c>
       <c r="K4" t="s" s="6">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="L4" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M4" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N4" t="s" s="6">
+        <v>579</v>
+      </c>
+      <c r="O4" t="s" s="6">
         <v>580</v>
-      </c>
-      <c r="O4" t="s" s="6">
-        <v>581</v>
       </c>
     </row>
     <row r="5">
@@ -2661,19 +2652,19 @@
         <v>77</v>
       </c>
       <c r="K5" t="s" s="6">
+        <v>584</v>
+      </c>
+      <c r="L5" t="s" s="6">
+        <v>25</v>
+      </c>
+      <c r="M5" t="s" s="6">
+        <v>578</v>
+      </c>
+      <c r="N5" t="s" s="6">
+        <v>579</v>
+      </c>
+      <c r="O5" t="s" s="6">
         <v>585</v>
-      </c>
-      <c r="L5" t="s" s="6">
-        <v>25</v>
-      </c>
-      <c r="M5" t="s" s="6">
-        <v>579</v>
-      </c>
-      <c r="N5" t="s" s="6">
-        <v>580</v>
-      </c>
-      <c r="O5" t="s" s="6">
-        <v>586</v>
       </c>
     </row>
     <row r="6">
@@ -2708,19 +2699,19 @@
         <v>85</v>
       </c>
       <c r="K6" t="s" s="6">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="L6" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M6" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N6" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O6" t="s" s="6">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="7">
@@ -2755,19 +2746,19 @@
         <v>93</v>
       </c>
       <c r="K7" t="s" s="6">
+        <v>587</v>
+      </c>
+      <c r="L7" t="s" s="6">
+        <v>25</v>
+      </c>
+      <c r="M7" t="s" s="6">
+        <v>578</v>
+      </c>
+      <c r="N7" t="s" s="6">
+        <v>579</v>
+      </c>
+      <c r="O7" t="s" s="6">
         <v>588</v>
-      </c>
-      <c r="L7" t="s" s="6">
-        <v>25</v>
-      </c>
-      <c r="M7" t="s" s="6">
-        <v>579</v>
-      </c>
-      <c r="N7" t="s" s="6">
-        <v>580</v>
-      </c>
-      <c r="O7" t="s" s="6">
-        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -2802,19 +2793,19 @@
         <v>102</v>
       </c>
       <c r="K8" t="s" s="6">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="L8" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M8" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N8" t="s" s="6">
+        <v>579</v>
+      </c>
+      <c r="O8" t="s" s="6">
         <v>580</v>
-      </c>
-      <c r="O8" t="s" s="6">
-        <v>581</v>
       </c>
     </row>
     <row r="9">
@@ -2849,19 +2840,19 @@
         <v>110</v>
       </c>
       <c r="K9" t="s" s="6">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="L9" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M9" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N9" t="s" s="6">
+        <v>579</v>
+      </c>
+      <c r="O9" t="s" s="6">
         <v>580</v>
-      </c>
-      <c r="O9" t="s" s="6">
-        <v>581</v>
       </c>
     </row>
     <row r="10">
@@ -2896,19 +2887,19 @@
         <v>118</v>
       </c>
       <c r="K10" t="s" s="6">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L10" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M10" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N10" t="s" s="6">
+        <v>579</v>
+      </c>
+      <c r="O10" t="s" s="6">
         <v>580</v>
-      </c>
-      <c r="O10" t="s" s="6">
-        <v>581</v>
       </c>
     </row>
     <row r="11">
@@ -2943,19 +2934,19 @@
         <v>126</v>
       </c>
       <c r="K11" t="s" s="6">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="L11" t="s" s="6">
-        <v>545</v>
+        <v>25</v>
       </c>
       <c r="M11" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N11" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O11" t="s" s="6">
-        <v>594</v>
+        <v>582</v>
       </c>
     </row>
     <row r="12">
@@ -2990,19 +2981,19 @@
         <v>134</v>
       </c>
       <c r="K12" t="s" s="6">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="L12" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M12" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N12" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O12" t="s" s="6">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="13">
@@ -3037,19 +3028,19 @@
         <v>143</v>
       </c>
       <c r="K13" t="s" s="6">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="L13" t="s" s="6">
-        <v>545</v>
+        <v>25</v>
       </c>
       <c r="M13" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N13" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O13" t="s" s="6">
-        <v>597</v>
+        <v>588</v>
       </c>
     </row>
     <row r="14">
@@ -3084,19 +3075,19 @@
         <v>151</v>
       </c>
       <c r="K14" t="s" s="6">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="L14" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M14" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N14" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O14" t="s" s="6">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="15">
@@ -3131,19 +3122,19 @@
         <v>159</v>
       </c>
       <c r="K15" t="s" s="6">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="L15" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M15" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N15" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O15" t="s" s="6">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="16">
@@ -3178,19 +3169,19 @@
         <v>168</v>
       </c>
       <c r="K16" t="s" s="6">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="L16" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M16" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N16" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O16" t="s" s="6">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="17">
@@ -3225,19 +3216,19 @@
         <v>176</v>
       </c>
       <c r="K17" t="s" s="6">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="L17" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M17" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N17" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O17" t="s" s="6">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="18">
@@ -3272,19 +3263,19 @@
         <v>184</v>
       </c>
       <c r="K18" t="s" s="6">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="L18" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M18" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N18" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O18" t="s" s="6">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="19">
@@ -3319,19 +3310,19 @@
         <v>192</v>
       </c>
       <c r="K19" t="s" s="6">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="L19" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M19" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N19" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O19" t="s" s="6">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="20">
@@ -3366,19 +3357,19 @@
         <v>200</v>
       </c>
       <c r="K20" t="s" s="6">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="L20" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M20" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N20" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O20" t="s" s="6">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="21">
@@ -3413,19 +3404,19 @@
         <v>208</v>
       </c>
       <c r="K21" t="s" s="6">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="L21" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M21" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N21" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O21" t="s" s="6">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="22">
@@ -3460,19 +3451,19 @@
         <v>216</v>
       </c>
       <c r="K22" t="s" s="6">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="L22" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M22" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N22" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O22" t="s" s="6">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="23">
@@ -3507,19 +3498,19 @@
         <v>224</v>
       </c>
       <c r="K23" t="s" s="6">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="L23" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M23" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N23" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O23" t="s" s="6">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="24">
@@ -3554,19 +3545,19 @@
         <v>232</v>
       </c>
       <c r="K24" t="s" s="6">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="L24" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M24" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N24" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O24" t="s" s="6">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="25">
@@ -3601,19 +3592,19 @@
         <v>240</v>
       </c>
       <c r="K25" t="s" s="6">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="L25" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M25" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N25" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O25" t="s" s="6">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="26">
@@ -3648,19 +3639,19 @@
         <v>248</v>
       </c>
       <c r="K26" t="s" s="6">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="L26" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M26" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N26" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O26" t="s" s="6">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="27">
@@ -3695,19 +3686,19 @@
         <v>256</v>
       </c>
       <c r="K27" t="s" s="6">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="L27" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M27" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N27" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O27" t="s" s="6">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="28">
@@ -3742,19 +3733,19 @@
         <v>264</v>
       </c>
       <c r="K28" t="s" s="6">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="L28" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M28" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N28" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O28" t="s" s="6">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="29">
@@ -3789,19 +3780,19 @@
         <v>272</v>
       </c>
       <c r="K29" t="s" s="6">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="L29" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M29" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N29" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O29" t="s" s="6">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="30">
@@ -3836,19 +3827,19 @@
         <v>280</v>
       </c>
       <c r="K30" t="s" s="6">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="L30" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M30" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N30" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O30" t="s" s="6">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="31">
@@ -3883,19 +3874,19 @@
         <v>289</v>
       </c>
       <c r="K31" t="s" s="6">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="L31" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M31" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N31" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O31" t="s" s="6">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="32">
@@ -3930,19 +3921,19 @@
         <v>297</v>
       </c>
       <c r="K32" t="s" s="6">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="L32" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M32" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N32" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O32" t="s" s="6">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="33">
@@ -3977,19 +3968,19 @@
         <v>305</v>
       </c>
       <c r="K33" t="s" s="6">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="L33" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M33" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N33" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O33" t="s" s="6">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="34">
@@ -4024,19 +4015,19 @@
         <v>314</v>
       </c>
       <c r="K34" t="s" s="6">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="L34" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M34" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N34" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O34" t="s" s="6">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="35">
@@ -4071,19 +4062,19 @@
         <v>322</v>
       </c>
       <c r="K35" t="s" s="6">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="L35" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M35" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N35" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O35" t="s" s="6">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="36">
@@ -4118,19 +4109,19 @@
         <v>330</v>
       </c>
       <c r="K36" t="s" s="6">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="L36" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M36" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N36" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O36" t="s" s="6">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="37">
@@ -4165,19 +4156,19 @@
         <v>339</v>
       </c>
       <c r="K37" t="s" s="6">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="L37" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M37" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N37" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O37" t="s" s="6">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="38">
@@ -4212,19 +4203,19 @@
         <v>347</v>
       </c>
       <c r="K38" t="s" s="6">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="L38" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M38" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N38" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O38" t="s" s="6">
-        <v>632</v>
+        <v>629</v>
       </c>
     </row>
     <row r="39">
@@ -4259,19 +4250,19 @@
         <v>356</v>
       </c>
       <c r="K39" t="s" s="6">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="L39" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M39" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N39" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O39" t="s" s="6">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="40">
@@ -4306,19 +4297,19 @@
         <v>364</v>
       </c>
       <c r="K40" t="s" s="6">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="L40" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M40" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N40" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O40" t="s" s="6">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="41">
@@ -4353,19 +4344,19 @@
         <v>373</v>
       </c>
       <c r="K41" t="s" s="6">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="L41" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M41" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N41" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O41" t="s" s="6">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="42">
@@ -4400,19 +4391,19 @@
         <v>381</v>
       </c>
       <c r="K42" t="s" s="6">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="L42" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M42" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N42" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O42" t="s" s="6">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="43">
@@ -4447,19 +4438,19 @@
         <v>389</v>
       </c>
       <c r="K43" t="s" s="6">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="L43" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M43" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N43" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O43" t="s" s="6">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="44">
@@ -4494,19 +4485,19 @@
         <v>397</v>
       </c>
       <c r="K44" t="s" s="6">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="L44" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M44" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N44" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O44" t="s" s="6">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="45">
@@ -4541,19 +4532,19 @@
         <v>405</v>
       </c>
       <c r="K45" t="s" s="6">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="L45" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M45" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N45" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O45" t="s" s="6">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="46">
@@ -4588,19 +4579,19 @@
         <v>414</v>
       </c>
       <c r="K46" t="s" s="6">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="L46" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M46" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N46" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O46" t="s" s="6">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="47">
@@ -4635,19 +4626,19 @@
         <v>422</v>
       </c>
       <c r="K47" t="s" s="6">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="L47" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M47" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N47" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O47" t="s" s="6">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="48">
@@ -4682,19 +4673,19 @@
         <v>430</v>
       </c>
       <c r="K48" t="s" s="6">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="L48" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M48" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N48" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O48" t="s" s="6">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="49">
@@ -4729,19 +4720,19 @@
         <v>437</v>
       </c>
       <c r="K49" t="s" s="6">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="L49" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M49" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N49" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O49" t="s" s="6">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="50">
@@ -4776,19 +4767,19 @@
         <v>445</v>
       </c>
       <c r="K50" t="s" s="6">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="L50" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M50" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N50" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O50" t="s" s="6">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="51">
@@ -4823,19 +4814,19 @@
         <v>453</v>
       </c>
       <c r="K51" t="s" s="6">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="L51" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M51" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N51" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O51" t="s" s="6">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="52">
@@ -4870,19 +4861,19 @@
         <v>461</v>
       </c>
       <c r="K52" t="s" s="6">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="L52" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M52" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N52" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O52" t="s" s="6">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="53">
@@ -4917,19 +4908,19 @@
         <v>469</v>
       </c>
       <c r="K53" t="s" s="6">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="L53" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M53" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N53" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O53" t="s" s="6">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="54">
@@ -4964,19 +4955,19 @@
         <v>477</v>
       </c>
       <c r="K54" t="s" s="6">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="L54" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M54" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N54" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O54" t="s" s="6">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="55">
@@ -5011,19 +5002,19 @@
         <v>485</v>
       </c>
       <c r="K55" t="s" s="6">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="L55" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M55" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N55" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O55" t="s" s="6">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="56">
@@ -5064,13 +5055,13 @@
         <v>53</v>
       </c>
       <c r="M56" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N56" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O56" t="s" s="6">
-        <v>654</v>
+        <v>651</v>
       </c>
     </row>
     <row r="57">
@@ -5105,19 +5096,19 @@
         <v>502</v>
       </c>
       <c r="K57" t="s" s="6">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="L57" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M57" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N57" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O57" t="s" s="6">
-        <v>656</v>
+        <v>653</v>
       </c>
     </row>
     <row r="58">
@@ -5152,19 +5143,19 @@
         <v>509</v>
       </c>
       <c r="K58" t="s" s="6">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="L58" t="s" s="6">
         <v>546</v>
       </c>
       <c r="M58" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N58" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O58" t="s" s="6">
-        <v>658</v>
+        <v>655</v>
       </c>
     </row>
     <row r="59">
@@ -5199,19 +5190,19 @@
         <v>515</v>
       </c>
       <c r="K59" t="s" s="6">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="L59" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M59" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N59" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O59" t="s" s="6">
-        <v>659</v>
+        <v>656</v>
       </c>
     </row>
     <row r="60">
@@ -5246,19 +5237,19 @@
         <v>522</v>
       </c>
       <c r="K60" t="s" s="6">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="L60" t="s" s="6">
         <v>546</v>
       </c>
       <c r="M60" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N60" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O60" t="s" s="6">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="61">
@@ -5293,19 +5284,19 @@
         <v>529</v>
       </c>
       <c r="K61" t="s" s="6">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="L61" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M61" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N61" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O61" t="s" s="6">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="62">
@@ -5340,19 +5331,19 @@
         <v>536</v>
       </c>
       <c r="K62" t="s" s="6">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="L62" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M62" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N62" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O62" t="s" s="6">
-        <v>665</v>
+        <v>662</v>
       </c>
     </row>
     <row r="63">
@@ -5387,19 +5378,19 @@
         <v>543</v>
       </c>
       <c r="K63" t="s" s="6">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="L63" t="s" s="6">
         <v>25</v>
       </c>
       <c r="M63" t="s" s="6">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N63" t="s" s="6">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O63" t="s" s="6">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
   </sheetData>
@@ -5469,11 +5460,11 @@
       </c>
       <c r="C2" t="n" s="7">
         <f>COUNTIFS('Cas de recette'!$B$2:$B$63,A2,'Cas de recette'!$L$2:$L$63,"OK")</f>
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="D2" t="n" s="7">
         <f>COUNTIFS('Cas de recette'!$B$2:$B$63,A2,'Cas de recette'!$L$2:$L$63,"KO")</f>
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E2" t="n" s="7">
         <f>COUNTIFS('Cas de recette'!$B$2:$B$63,A2,'Cas de recette'!$L$2:$L$63,"Bloqué")</f>
@@ -5485,7 +5476,7 @@
       </c>
       <c r="G2" t="n" s="8">
         <f>IF(B2=0,0,C2/B2)</f>
-        <v>0.9230769230769231</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="3">
@@ -5498,11 +5489,11 @@
       </c>
       <c r="C3" t="n" s="7">
         <f>COUNTIFS('Cas de recette'!$B$2:$B$63,A3,'Cas de recette'!$L$2:$L$63,"OK")</f>
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D3" t="n" s="7">
         <f>COUNTIFS('Cas de recette'!$B$2:$B$63,A3,'Cas de recette'!$L$2:$L$63,"KO")</f>
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E3" t="n" s="7">
         <f>COUNTIFS('Cas de recette'!$B$2:$B$63,A3,'Cas de recette'!$L$2:$L$63,"Bloqué")</f>
@@ -5514,7 +5505,7 @@
       </c>
       <c r="G3" t="n" s="8">
         <f>IF(B3=0,0,C3/B3)</f>
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="4">
@@ -5701,11 +5692,11 @@
       </c>
       <c r="C10" t="n" s="9">
         <f>SUM(C2:C9)</f>
-        <v>57.0</v>
+        <v>59.0</v>
       </c>
       <c r="D10" t="n" s="9">
         <f>SUM(D2:D9)</f>
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="E10" t="n" s="9">
         <f>SUM(E2:E9)</f>
@@ -5717,7 +5708,7 @@
       </c>
       <c r="G10" t="n" s="8">
         <f>IF(B10=0,0,C10/B10)</f>
-        <v>0.9193548387096774</v>
+        <v>0.9516129032258065</v>
       </c>
     </row>
     <row r="12">
@@ -5778,7 +5769,7 @@
         <v>558</v>
       </c>
       <c r="D2" t="s" s="5">
-        <v>559</v>
+        <v>497</v>
       </c>
       <c r="E2" t="s" s="6">
         <v>52</v>
@@ -5792,16 +5783,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="5">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B3" t="s" s="5">
         <v>424</v>
       </c>
       <c r="C3" t="s" s="5">
+        <v>560</v>
+      </c>
+      <c r="D3" t="s" s="5">
         <v>561</v>
-      </c>
-      <c r="D3" t="s" s="5">
-        <v>562</v>
       </c>
       <c r="E3" t="s" s="6">
         <v>52</v>
@@ -5815,16 +5806,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="5">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B4" t="s" s="5">
         <v>432</v>
       </c>
       <c r="C4" t="s" s="5">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D4" t="s" s="5">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E4" t="s" s="6">
         <v>52</v>
@@ -5838,16 +5829,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="5">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B5" t="s" s="5">
         <v>358</v>
       </c>
       <c r="C5" t="s" s="5">
+        <v>565</v>
+      </c>
+      <c r="D5" t="s" s="5">
         <v>566</v>
-      </c>
-      <c r="D5" t="s" s="5">
-        <v>567</v>
       </c>
       <c r="E5" t="s" s="6">
         <v>52</v>
@@ -5861,13 +5852,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="5">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B6" t="s" s="5">
         <v>202</v>
       </c>
       <c r="C6" t="s" s="5">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D6" t="s" s="5">
         <v>497</v>
@@ -5884,16 +5875,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="5">
+        <v>569</v>
+      </c>
+      <c r="B7" t="s" s="5">
         <v>570</v>
       </c>
-      <c r="B7" t="s" s="5">
+      <c r="C7" t="s" s="5">
         <v>571</v>
       </c>
-      <c r="C7" t="s" s="5">
+      <c r="D7" t="s" s="5">
         <v>572</v>
-      </c>
-      <c r="D7" t="s" s="5">
-        <v>573</v>
       </c>
       <c r="E7" t="s" s="6">
         <v>52</v>
@@ -5907,16 +5898,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="5">
+        <v>573</v>
+      </c>
+      <c r="B8" t="s" s="5">
         <v>574</v>
       </c>
-      <c r="B8" t="s" s="5">
+      <c r="C8" t="s" s="5">
         <v>575</v>
       </c>
-      <c r="C8" t="s" s="5">
+      <c r="D8" t="s" s="5">
         <v>576</v>
-      </c>
-      <c r="D8" t="s" s="5">
-        <v>577</v>
       </c>
       <c r="E8" t="s" s="6">
         <v>52</v>
